--- a/docs/requirements-v1.03.xlsx
+++ b/docs/requirements-v1.03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57BCF53-98F4-4DEC-9215-8C2C3727EB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55C3221-2711-4C58-855E-3E8B2F092AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="14610" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="14610" windowHeight="7845" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="232">
   <si>
     <t>チーム名:</t>
   </si>
@@ -1025,13 +1025,6 @@
 ・リンクが1つもない日は、行ごと出さない</t>
   </si>
   <si>
-    <t>要検討</t>
-  </si>
-  <si>
-    <t>済:どこに出すか → ゲージのすぐ下(基本設計 Q27)
-・実装優先度(Must か Should か)</t>
-  </si>
-  <si>
     <t>基本設計 トップの画面で本人の希望(主に授業で使う)・Q27</t>
   </si>
   <si>
@@ -1072,6 +1065,11 @@
   </si>
   <si>
     <t>ver.1.03</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:どこに出すか → ゲージのすぐ下(基本設計 Q27)
+済:実装優先度 → Must。作る順番の①に入れる</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1141,7 +1139,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1156,12 +1154,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCD5B4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1324,9 +1316,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1346,6 +1335,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1355,14 +1347,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1687,62 +1679,62 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="54" customHeight="1">
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="8" spans="1:10" ht="19.5">
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
     </row>
     <row r="10" spans="1:10" ht="19.5">
       <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="37.5">
-      <c r="F13" s="18" t="s">
-        <v>232</v>
+      <c r="F13" s="33" t="s">
+        <v>230</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5">
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19" t="s">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" ht="16.5">
       <c r="E16" s="3" t="s">
@@ -1821,32 +1813,32 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="25" t="s">
+      <c r="E5" s="26"/>
+      <c r="F5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="25" t="s">
+      <c r="G5" s="26"/>
+      <c r="H5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" ht="16.5">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
@@ -1946,14 +1938,14 @@
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>230</v>
+      <c r="B11" s="31" t="s">
+        <v>228</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="33">
+      <c r="E11" s="32">
         <v>46312</v>
       </c>
       <c r="F11" s="4"/>
@@ -2201,7 +2193,7 @@
         <v>40</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2698,14 +2690,14 @@
       <c r="D26" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="G26" s="30" t="s">
         <v>220</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2812,13 +2804,13 @@
         <v>56</v>
       </c>
       <c r="B7" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>223</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="132">
@@ -2829,7 +2821,7 @@
         <v>58</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>59</v>
@@ -2843,7 +2835,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>61</v>
@@ -2871,7 +2863,7 @@
         <v>67</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>141</v>
